--- a/Data files/metadata_EP_SAR.xlsx
+++ b/Data files/metadata_EP_SAR.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ucliveac-my.sharepoint.com/personal/rose_foster-dyer_canterbury_ac_nz/Documents/PostDoc/Population modelling/Final data files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ucliveac-my.sharepoint.com/personal/rose_foster-dyer_canterbury_ac_nz/Documents/Github/SAR_EmperorPenguin/Data files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="8_{72C2E6A5-41DE-4F76-9D79-EA77E43670C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38FF096D-FD87-46EA-BB1D-4D9CACCF303B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B57385E-2B44-4D02-92C2-93F7CDE64907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{43DCBBA1-D0D5-4C0F-B147-9F0C9D19039C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{43DCBBA1-D0D5-4C0F-B147-9F0C9D19039C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="183">
   <si>
     <t xml:space="preserve">site </t>
   </si>
@@ -146,22 +147,6 @@
     <t>medium: birds were able to be located without the use of optical imagery but required many images to compare</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">ease of observation metric </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(response variable for models)</t>
-    </r>
-  </si>
-  <si>
     <t>grazing angle of image task</t>
   </si>
   <si>
@@ -369,9 +354,6 @@
     <t>Ta_C</t>
   </si>
   <si>
-    <t xml:space="preserve">Column names in dfHuddle </t>
-  </si>
-  <si>
     <t>date_first</t>
   </si>
   <si>
@@ -426,18 +408,6 @@
     <t>mean_range_pct</t>
   </si>
   <si>
-    <t>lower coefficient uncertainty (derived from Winterl bayesian model), same values applied to all observations</t>
-  </si>
-  <si>
-    <t>upper coefficient uncertainty (derived from Winterl bayesian model), same values applied to all observations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">total coefficent standard error, summed directlty </t>
-  </si>
-  <si>
-    <t xml:space="preserve">standard deviation around the mean of 'male huddle' observations if more than one image was captured </t>
-  </si>
-  <si>
     <t>description</t>
   </si>
   <si>
@@ -492,7 +462,130 @@
     <t>total count of all mean of 'male huddle' individual counts</t>
   </si>
   <si>
-    <t>total count of all median of 'male huddle' individual counts</t>
+    <t>estimated phenological stage based on huddle appearance, area covered and date (male huddle, females present, female return)</t>
+  </si>
+  <si>
+    <t>indicated if the area calculated for this image was removed, often due to the birds being too dispersed (often after female return) to accurately quantify. Removed data were not analysed and did not contribute to the breeding estimate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">estimated density of the huddles based on the era5 weather reanalysis data and the windchill model </t>
+  </si>
+  <si>
+    <t>estimate number of birds calculated by multiply the area of huddles by the predicted density (rho_pred)</t>
+  </si>
+  <si>
+    <t>the lower estimated density bound based on the reported coefficient of each weather coefficient in Winterl et al. 2024</t>
+  </si>
+  <si>
+    <t>the upper estimated density bound based on the reported coefficient of each weather coefficient in Winterl et al. 2024</t>
+  </si>
+  <si>
+    <t>the upper count bound, calculated by multiplying the rho_upper by the area of huddles to give the upper uncertainity estimate of number of birds in each image</t>
+  </si>
+  <si>
+    <t>the lower count bound, calculated by muliplying the rho_lower by the area of huddles to give the lower uncertainity estimate of number of birds in each image</t>
+  </si>
+  <si>
+    <t>the apparent temperature, the temperature estimated to be experienced by the birds, understanding the effect that windspeed, humidity and radiation has on the temperature</t>
+  </si>
+  <si>
+    <t>Column names in dfHuddle (dataset of male huddle summary data)</t>
+  </si>
+  <si>
+    <t>date of first image determined to represent the male huddle</t>
+  </si>
+  <si>
+    <t>date of the last image determined to represent the male huddle</t>
+  </si>
+  <si>
+    <t>mean day of year value for the imagery determined to represent the male huddle</t>
+  </si>
+  <si>
+    <t>number of images per location that were classed as male huddle</t>
+  </si>
+  <si>
+    <t>qualitative determinate of quality of estimate based on number of observations, single obs = 1, low n = 2, good = &gt;3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean number of individuals estimated using the density model across all imagery that was determined to be male huddle for that location </t>
+  </si>
+  <si>
+    <t>median number of individuals estimated using the density model across all imagery that was determined to be male huddle for that location (we used mean as some locations had only one or two estimates and median was not able to be used across all sites)</t>
+  </si>
+  <si>
+    <t>lower coefficient uncertainty (values reported in Winterl et al. 2024), same values were applied to all observations</t>
+  </si>
+  <si>
+    <t>upper coefficient uncertainty (values reported in Winterl et al. 2024), same values applied to all observations</t>
+  </si>
+  <si>
+    <t>the plus or minus standard error calculated for each estimated density based on the coefficient uncertainty reported in Winterl et al. 2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">standard deviation of the number of individuals estimated from 'male huddle' observations, indicating variability between observation. Only available if more than one male huddle image was captured </t>
+  </si>
+  <si>
+    <t>standard error around the mean of the number of individuals estimated from 'male huddle' observations, indicating uncertainty in breeding estimate based on how many images were captured, only available if more than one male huddle image was captured</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lower bounds of the observation based uncertainty interval, calculated by minusing obs_sem from count_mean </t>
+  </si>
+  <si>
+    <t xml:space="preserve">upper bounds of the observation based uncertainity interval, calculated by adding obs_sem to count_mean </t>
+  </si>
+  <si>
+    <t xml:space="preserve">combined standard error which combined both sources of uncertainty (coefficient uncertainity and observation variance). Values were added in quadrature to produce a more conservation uncertainty estimate. If only one male huddle image was acquired, combined_se_pm is equal to coeff_se_pm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">lower bounds of combined uncertainity, calculated by minusing combined_se_pm from count_mean </t>
+  </si>
+  <si>
+    <t xml:space="preserve">upper bounds of the combined uncertainty, calculated by adding combined_se_pm to count_mean </t>
+  </si>
+  <si>
+    <t>the total combined uncertainty range, indicating a scale-independent measure of relative uncertainty for each colony estimate, calculated by multiplying combined_se_pm by 2 and expressed as a percentage of count_mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total breeding population (all 55 colonies combined) </t>
+  </si>
+  <si>
+    <t>year of estimate 2025</t>
+  </si>
+  <si>
+    <t>number of colonies estimated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">how many of the 55 colonies had atleast 3 observations of male huddle imagery </t>
+  </si>
+  <si>
+    <t xml:space="preserve">how many of the 55 colonies had only 2 observations of male huddle imagery </t>
+  </si>
+  <si>
+    <t xml:space="preserve">how many of the 55 colonies had a single observation of male huddle imagery </t>
+  </si>
+  <si>
+    <t xml:space="preserve">total uncertainty derived from the windchill model weather coefficients (reported by Winterl et al. 2024). This is treated as systematic error source, applying the same error to all colonies. Calculated by summing the coeff_se from all colonies, as the coefficient errors are correlated across colonies and will act in the same direction at all sites. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">total uncertainty derived from the observation error, from the variation is SAR observations at each colony when multiple male huddle images were available. This is treated as a random error source as each obs error is independent between colonies. Calculated by combining obs_se in quadrature across all colonies to account for this. </t>
+  </si>
+  <si>
+    <t>total combined standard error for the global breeding estimate, representing the best estimate of total uncertainity in accounting for the two different sources of error. Calculated by summing the systematic coefficient uncertainity directly and combining it with random obseration uncertainity to quadrature.</t>
+  </si>
+  <si>
+    <t>combined standard error expressed as percentage of total_count_mean</t>
+  </si>
+  <si>
+    <t>lower bound of the estimate total count, representing an approximate 68% uncertainity interval, calculated as total_count_mean minus combined_se</t>
+  </si>
+  <si>
+    <t>upper bound of the estimated total count, representing an approximate 68% uncertainity interval, calculated as total_count_mean plus combined_se</t>
+  </si>
+  <si>
+    <t>upper 95% confidence interval, assuming the total population estimate is normall distributed. Calculated as total_count_mean plus 1.96 times combined_se</t>
+  </si>
+  <si>
+    <t>lower 95% confidence interval, assuming the total population estimate is normally distributed. Calculated as total_count_mean minus 1.96 times combined_se</t>
   </si>
 </sst>
 </file>
@@ -941,7 +1034,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -970,10 +1063,10 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" t="s">
         <v>49</v>
-      </c>
-      <c r="B10" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -989,7 +1082,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -1037,7 +1130,7 @@
         <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -1045,7 +1138,7 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -1053,7 +1146,7 @@
         <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -1061,7 +1154,7 @@
         <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -1069,7 +1162,7 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -1077,7 +1170,7 @@
         <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -1085,7 +1178,7 @@
         <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -1093,7 +1186,7 @@
         <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -1101,7 +1194,7 @@
         <v>18</v>
       </c>
       <c r="B26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -1109,7 +1202,7 @@
         <v>19</v>
       </c>
       <c r="B27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -1117,7 +1210,7 @@
         <v>20</v>
       </c>
       <c r="B28" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -1125,20 +1218,20 @@
         <v>21</v>
       </c>
       <c r="B29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B32" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -1146,15 +1239,15 @@
         <v>1</v>
       </c>
       <c r="B33" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B34" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -1162,7 +1255,7 @@
         <v>4</v>
       </c>
       <c r="B35" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -1191,10 +1284,10 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B39" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -1223,18 +1316,18 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>48</v>
+      </c>
+      <c r="B43" t="s">
         <v>49</v>
-      </c>
-      <c r="B43" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B44" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -1242,15 +1335,15 @@
         <v>9</v>
       </c>
       <c r="B45" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B46" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -1258,47 +1351,47 @@
         <v>11</v>
       </c>
       <c r="B47" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B48" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B50" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B51" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B52" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -1306,7 +1399,7 @@
         <v>15</v>
       </c>
       <c r="B53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -1314,549 +1407,774 @@
         <v>19</v>
       </c>
       <c r="B54" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B55" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B56" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B57" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B58" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B59" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B60" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B61" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B62" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B63" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B64" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B65" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B66" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B67" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>52</v>
+        <v>51</v>
+      </c>
+      <c r="B71" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>1</v>
       </c>
+      <c r="B72" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>53</v>
+        <v>52</v>
+      </c>
+      <c r="B73" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>4</v>
       </c>
+      <c r="B74" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>5</v>
       </c>
+      <c r="B75" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>7</v>
       </c>
+      <c r="B76" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>6</v>
       </c>
+      <c r="B77" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>54</v>
+        <v>53</v>
+      </c>
+      <c r="B78" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>8</v>
       </c>
+      <c r="B79" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B80" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B81" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>48</v>
+      </c>
+      <c r="B82" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+      <c r="B83" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>96</v>
+      </c>
+      <c r="B84" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B85" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B86" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+      <c r="B87" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B88" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>56</v>
+      </c>
+      <c r="B89" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
+      <c r="B90" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
+      <c r="B91" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
+      <c r="B92" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B93" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B94" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B95" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>61</v>
+      </c>
+      <c r="B96" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
+      <c r="B97" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
+      <c r="B98" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
+      <c r="B99" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
+      <c r="B100" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
+      <c r="B101" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
+      <c r="B102" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
+      <c r="B103" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
+      <c r="B104" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
+      <c r="B105" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
+      <c r="B106" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
+      <c r="B107" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B108" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
+        <v>98</v>
+      </c>
+      <c r="B109" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
+      <c r="B110" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
+      <c r="B111" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
+      <c r="B112" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
+      <c r="B113" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
+      <c r="B114" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B115" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+      <c r="B119" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B120" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B121" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
+        <v>105</v>
+      </c>
+      <c r="B122" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>106</v>
+      </c>
+      <c r="B123" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
+      <c r="B124" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
+      <c r="B125" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
+      <c r="B126" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
+      <c r="B127" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
-        <v>113</v>
+      <c r="B128" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B129" t="s">
-        <v>125</v>
+        <v>158</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B130" t="s">
-        <v>126</v>
+        <v>159</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B131" t="s">
-        <v>127</v>
+        <v>160</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B132" t="s">
-        <v>128</v>
+        <v>161</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>118</v>
+        <v>116</v>
+      </c>
+      <c r="B133" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>119</v>
+        <v>117</v>
+      </c>
+      <c r="B134" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>120</v>
+        <v>118</v>
+      </c>
+      <c r="B135" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>121</v>
+        <v>119</v>
+      </c>
+      <c r="B136" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>122</v>
+        <v>120</v>
+      </c>
+      <c r="B137" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>123</v>
+        <v>121</v>
+      </c>
+      <c r="B138" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>124</v>
+        <v>122</v>
+      </c>
+      <c r="B139" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>129</v>
+        <v>123</v>
+      </c>
+      <c r="B142" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>130</v>
+        <v>124</v>
+      </c>
+      <c r="B143" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>131</v>
+        <v>125</v>
+      </c>
+      <c r="B144" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>132</v>
+        <v>126</v>
+      </c>
+      <c r="B145" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>133</v>
+        <v>127</v>
+      </c>
+      <c r="B146" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>134</v>
+        <v>128</v>
+      </c>
+      <c r="B147" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B148" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B149" t="s">
-        <v>147</v>
+        <v>175</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>137</v>
+        <v>131</v>
+      </c>
+      <c r="B150" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>138</v>
+        <v>132</v>
+      </c>
+      <c r="B151" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>139</v>
+        <v>133</v>
+      </c>
+      <c r="B152" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>140</v>
+        <v>134</v>
+      </c>
+      <c r="B153" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>141</v>
+        <v>135</v>
+      </c>
+      <c r="B154" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>142</v>
+        <v>136</v>
+      </c>
+      <c r="B155" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>143</v>
+        <v>137</v>
+      </c>
+      <c r="B156" t="s">
+        <v>181</v>
       </c>
     </row>
   </sheetData>

--- a/Data files/metadata_EP_SAR.xlsx
+++ b/Data files/metadata_EP_SAR.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,13 +10,12 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{7B57385E-2B44-4D02-92C2-93F7CDE64907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{43DCBBA1-D0D5-4C0F-B147-9F0C9D19039C}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{43DCBBA1-D0D5-4C0F-B147-9F0C9D19039C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>

--- a/Data files/metadata_EP_SAR.xlsx
+++ b/Data files/metadata_EP_SAR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ucliveac-my.sharepoint.com/personal/rose_foster-dyer_canterbury_ac_nz/Documents/Github/SAR_EmperorPenguin/Data files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B57385E-2B44-4D02-92C2-93F7CDE64907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="8_{7B57385E-2B44-4D02-92C2-93F7CDE64907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12B595E1-790A-40EF-AEFF-8ABC2B281208}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{43DCBBA1-D0D5-4C0F-B147-9F0C9D19039C}"/>
+    <workbookView xWindow="28695" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{43DCBBA1-D0D5-4C0F-B147-9F0C9D19039C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="232">
   <si>
     <t xml:space="preserve">site </t>
   </si>
@@ -440,18 +440,6 @@
     <t>combined_se_pct</t>
   </si>
   <si>
-    <t>lower_1se</t>
-  </si>
-  <si>
-    <t>upper_1se</t>
-  </si>
-  <si>
-    <t>lower_95ci</t>
-  </si>
-  <si>
-    <t>upper_95ci</t>
-  </si>
-  <si>
     <t>Column names of total_population_summary</t>
   </si>
   <si>
@@ -575,23 +563,289 @@
     <t>combined standard error expressed as percentage of total_count_mean</t>
   </si>
   <si>
-    <t>lower bound of the estimate total count, representing an approximate 68% uncertainity interval, calculated as total_count_mean minus combined_se</t>
-  </si>
-  <si>
-    <t>upper bound of the estimated total count, representing an approximate 68% uncertainity interval, calculated as total_count_mean plus combined_se</t>
-  </si>
-  <si>
-    <t>upper 95% confidence interval, assuming the total population estimate is normall distributed. Calculated as total_count_mean plus 1.96 times combined_se</t>
-  </si>
-  <si>
-    <t>lower 95% confidence interval, assuming the total population estimate is normally distributed. Calculated as total_count_mean minus 1.96 times combined_se</t>
+    <t>EP_Chick_counts.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">colony_full </t>
+  </si>
+  <si>
+    <t>count</t>
+  </si>
+  <si>
+    <t>age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">credit </t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">full name of colony </t>
+  </si>
+  <si>
+    <t xml:space="preserve">shortened name of colony </t>
+  </si>
+  <si>
+    <t xml:space="preserve">four letter code for colony name </t>
+  </si>
+  <si>
+    <t>number of penguins counted</t>
+  </si>
+  <si>
+    <t>year of count</t>
+  </si>
+  <si>
+    <t>date count was undertaken</t>
+  </si>
+  <si>
+    <t xml:space="preserve">season count was undertaken </t>
+  </si>
+  <si>
+    <t xml:space="preserve">age of the birds counted (adult or chick) </t>
+  </si>
+  <si>
+    <t>who performed the count and provided the data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">additional information about each observation </t>
+  </si>
+  <si>
+    <t>est_size_AllColonies.csv</t>
+  </si>
+  <si>
+    <t>colony_x</t>
+  </si>
+  <si>
+    <t>site_name</t>
+  </si>
+  <si>
+    <t>avg_size-sd</t>
+  </si>
+  <si>
+    <t>source</t>
+  </si>
+  <si>
+    <t>years</t>
+  </si>
+  <si>
+    <t>n_years</t>
+  </si>
+  <si>
+    <t>method</t>
+  </si>
+  <si>
+    <t>full colony name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shortened colony name </t>
+  </si>
+  <si>
+    <t xml:space="preserve">average size of that colony based on best available (longest timeseries) data </t>
+  </si>
+  <si>
+    <t>standard deviation of the average size of the best available estimate</t>
+  </si>
+  <si>
+    <t>publication that provided the longest time series data for that site</t>
+  </si>
+  <si>
+    <t>year range that contributed to the average size reported</t>
+  </si>
+  <si>
+    <t>number of years within the year range that contributed to the estimated average size</t>
+  </si>
+  <si>
+    <r>
+      <t>method used to estimate the abundance of the site. (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>VHR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> refers to ver high resolution satellite imagery and a bayesian population model,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Sentinel-2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">refers to estimated size based on low resolution imagery as high-res is yet to be available for newly discovered colonies, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">VHR count </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">is when individual birds were counted in VHR imagery - not analysed using supervised classification and bayesian model, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>VHR estimate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> is uses previous linear model approach that estimates ~1 penguin per m2, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>aerial count</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> refers to on the ground observation of the location, where researchers flew over, took photos and counted the number of birds visible in the photos. *Note, only "VHR" average size values were compared against our SAR-derived estimates.</t>
+    </r>
+  </si>
+  <si>
+    <t>site_number</t>
+  </si>
+  <si>
+    <t>N_mean</t>
+  </si>
+  <si>
+    <t>N_se</t>
+  </si>
+  <si>
+    <t>N_q025</t>
+  </si>
+  <si>
+    <t>N_q05</t>
+  </si>
+  <si>
+    <t>N_median</t>
+  </si>
+  <si>
+    <t>N_q95</t>
+  </si>
+  <si>
+    <t>N_q975</t>
+  </si>
+  <si>
+    <t>LaRue_etal2024_colony_results09-18.csv</t>
+  </si>
+  <si>
+    <t>year of estimate</t>
+  </si>
+  <si>
+    <t>site number (referring to colony name)</t>
+  </si>
+  <si>
+    <t>standard error around the estimated number of adult emperor penguins on the ice in springtime</t>
+  </si>
+  <si>
+    <t>lower 2.5% confidence interval for the 95% CI</t>
+  </si>
+  <si>
+    <t>lower 5% CI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">estimated number of adult emperor penguins on the ice in springtime derived from colony areas and a bayesian population model </t>
+  </si>
+  <si>
+    <t>median number of adult emperor penguins on the ice in springtime, derived from colony areas and a bayesian population model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upper 5% confidence interval </t>
+  </si>
+  <si>
+    <t xml:space="preserve">upper 2.5% confidence interval, comtributing to the total 95% CI around the estimated number of adult emperor penguins on the ice in springtime at each location </t>
+  </si>
+  <si>
+    <t xml:space="preserve">four letter code for the colony name </t>
+  </si>
+  <si>
+    <t xml:space="preserve">the name of the colony </t>
+  </si>
+  <si>
+    <t>latitude of the colony (location)</t>
+  </si>
+  <si>
+    <t>longitude of the colony (location)</t>
+  </si>
+  <si>
+    <t>Foster-Dyer_etal2026_RS_00-2024.csv</t>
+  </si>
+  <si>
+    <t>Fretwell_etal2025_WS09-23.csv</t>
+  </si>
+  <si>
+    <t>sar_huddles_20250502_ERA5_v3_grouped_era5added.csv</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -602,6 +856,14 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -646,11 +908,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -985,14 +1251,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D70080DA-7C67-4F2D-B6FD-EB290D3A5469}">
-  <dimension ref="A1:B156"/>
+  <dimension ref="A1:B194"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="3" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1081,7 +1347,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -1225,955 +1491,1209 @@
         <v>74</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>51</v>
-      </c>
-      <c r="B32" t="s">
-        <v>75</v>
+    <row r="32" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="5" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="B33" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="B34" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="B35" t="s">
-        <v>50</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B36" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B37" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B38" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>53</v>
+        <v>6</v>
       </c>
       <c r="B39" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>8</v>
+        <v>53</v>
       </c>
       <c r="B40" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B41" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B42" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="B43" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B44" t="s">
-        <v>93</v>
+        <v>49</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="B45" t="s">
-        <v>139</v>
+        <v>93</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="B46" t="s">
-        <v>36</v>
+        <v>135</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="B47" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="B48" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B49" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B50" t="s">
-        <v>80</v>
+        <v>40</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B51" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B52" t="s">
-        <v>39</v>
+        <v>79</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="B53" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B54" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="B55" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B57" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B58" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B59" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B60" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B62" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B64" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B65" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B66" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>72</v>
+      </c>
+      <c r="B67" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
         <v>73</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B68" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" s="3" t="s">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
         <v>95</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>51</v>
-      </c>
-      <c r="B71" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="B72" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="B73" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="B74" t="s">
-        <v>50</v>
+        <v>94</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B75" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B76" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B77" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>53</v>
+        <v>6</v>
       </c>
       <c r="B78" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>8</v>
+        <v>53</v>
       </c>
       <c r="B79" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B80" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B81" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="B82" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B83" t="s">
-        <v>93</v>
+        <v>49</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>96</v>
+        <v>54</v>
       </c>
       <c r="B84" t="s">
-        <v>141</v>
+        <v>93</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B85" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>9</v>
+        <v>97</v>
       </c>
       <c r="B86" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="B87" t="s">
-        <v>36</v>
+        <v>135</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="B88" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="B89" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B90" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B91" t="s">
-        <v>80</v>
+        <v>40</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B92" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B93" t="s">
-        <v>39</v>
+        <v>79</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="B94" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B95" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="B96" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B97" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B98" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B99" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B100" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B101" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B102" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B103" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B104" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B105" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B106" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B107" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B108" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="B109" t="s">
-        <v>143</v>
+        <v>82</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B110" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B111" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B112" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B113" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B114" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>103</v>
+      </c>
+      <c r="B115" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
         <v>104</v>
       </c>
-      <c r="B115" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A118" s="3" t="s">
-        <v>150</v>
+      <c r="B116" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
-        <v>51</v>
-      </c>
-      <c r="B119" t="s">
-        <v>75</v>
+      <c r="A119" s="3" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="B120" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B121" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>105</v>
+        <v>3</v>
       </c>
       <c r="B122" t="s">
-        <v>151</v>
+        <v>26</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B123" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B124" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B125" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B126" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B127" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B128" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B129" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B130" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B131" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B132" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B133" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B134" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B135" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B136" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B137" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B138" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
+        <v>121</v>
+      </c>
+      <c r="B139" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
         <v>122</v>
       </c>
-      <c r="B139" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A141" s="3" t="s">
-        <v>138</v>
+      <c r="B140" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
-        <v>123</v>
-      </c>
-      <c r="B142" t="s">
-        <v>169</v>
+      <c r="A142" s="3" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B143" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B144" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B145" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B146" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B147" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B148" t="s">
-        <v>140</v>
+        <v>170</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B149" t="s">
-        <v>175</v>
+        <v>136</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B150" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B151" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B152" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B153" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A154" t="s">
-        <v>135</v>
-      </c>
-      <c r="B154" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A155" t="s">
-        <v>136</v>
-      </c>
-      <c r="B155" t="s">
-        <v>182</v>
+      <c r="A155" s="3" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>137</v>
+        <v>176</v>
       </c>
       <c r="B156" t="s">
         <v>181</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>51</v>
+      </c>
+      <c r="B157" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>1</v>
+      </c>
+      <c r="B158" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A159" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B159" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>53</v>
+      </c>
+      <c r="B160" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>5</v>
+      </c>
+      <c r="B161" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>124</v>
+      </c>
+      <c r="B162" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>178</v>
+      </c>
+      <c r="B163" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>179</v>
+      </c>
+      <c r="B164" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>180</v>
+      </c>
+      <c r="B165" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A168" s="5" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>1</v>
+      </c>
+      <c r="B169" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>192</v>
+      </c>
+      <c r="B170" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>193</v>
+      </c>
+      <c r="B171" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>48</v>
+      </c>
+      <c r="B172" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>194</v>
+      </c>
+      <c r="B173" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>195</v>
+      </c>
+      <c r="B174" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>196</v>
+      </c>
+      <c r="B175" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>197</v>
+      </c>
+      <c r="B176" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>198</v>
+      </c>
+      <c r="B177" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A179" s="5" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A180" s="5" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A181" s="5" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>53</v>
+      </c>
+      <c r="B182" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>207</v>
+      </c>
+      <c r="B183" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>208</v>
+      </c>
+      <c r="B184" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>209</v>
+      </c>
+      <c r="B185" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>210</v>
+      </c>
+      <c r="B186" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>211</v>
+      </c>
+      <c r="B187" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>212</v>
+      </c>
+      <c r="B188" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>213</v>
+      </c>
+      <c r="B189" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>214</v>
+      </c>
+      <c r="B190" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>1</v>
+      </c>
+      <c r="B191" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>193</v>
+      </c>
+      <c r="B192" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>2</v>
+      </c>
+      <c r="B193" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>3</v>
+      </c>
+      <c r="B194" t="s">
+        <v>228</v>
       </c>
     </row>
   </sheetData>

--- a/Data files/metadata_EP_SAR.xlsx
+++ b/Data files/metadata_EP_SAR.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="57" documentId="8_{7B57385E-2B44-4D02-92C2-93F7CDE64907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12B595E1-790A-40EF-AEFF-8ABC2B281208}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{43DCBBA1-D0D5-4C0F-B147-9F0C9D19039C}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{43DCBBA1-D0D5-4C0F-B147-9F0C9D19039C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
